--- a/დეკლარაცია დელივერერს.xlsx
+++ b/დეკლარაცია დელივერერს.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nana\deliverer\დეკლარაცია\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nana\bank-summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BE49C1-3A19-46D5-8CEE-F94BC6CD1E19}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2185830-67FA-4156-B4E0-51ECD6042D56}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" tabRatio="889" firstSheet="30" activeTab="43" xr2:uid="{262C77A9-C0EF-4E18-A530-ED4A8457AF6E}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" tabRatio="889" firstSheet="30" activeTab="44" xr2:uid="{262C77A9-C0EF-4E18-A530-ED4A8457AF6E}"/>
   </bookViews>
   <sheets>
     <sheet name="კალკულაცია აგვისტო" sheetId="3" r:id="rId1"/>
@@ -57,6 +57,7 @@
     <sheet name="თებ 26" sheetId="44" r:id="rId42"/>
     <sheet name="მარ 26" sheetId="45" r:id="rId43"/>
     <sheet name="აპრილი 26" sheetId="46" r:id="rId44"/>
+    <sheet name="მაისი 26" sheetId="47" r:id="rId45"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -68,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="69">
   <si>
     <t>დელივერერს</t>
   </si>
@@ -533,7 +534,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -594,6 +595,8 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="43" fontId="3" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -4837,6 +4840,119 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64830BCA-104F-4991-A600-861B38927D21}">
+  <dimension ref="B5:I15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="2:9">
+      <c r="B5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="4">
+        <v>73348.649999999994</v>
+      </c>
+      <c r="D5" s="5">
+        <f>C5/1.18</f>
+        <v>62159.872881355928</v>
+      </c>
+      <c r="E5" s="4">
+        <f>D5*0.18</f>
+        <v>11188.777118644066</v>
+      </c>
+      <c r="G5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="5">
+        <v>10915</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="4">
+        <f>E5-C9</f>
+        <v>10915.527118644066</v>
+      </c>
+      <c r="G6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4">
+        <v>75.83</v>
+      </c>
+      <c r="D7" s="56"/>
+      <c r="E7" s="4"/>
+      <c r="G7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" spans="2:9">
+      <c r="B8" s="4"/>
+      <c r="C8" s="4">
+        <v>197.42</v>
+      </c>
+      <c r="D8" s="56"/>
+      <c r="E8" s="4"/>
+      <c r="H8" s="58">
+        <f>SUM(H5:H7)</f>
+        <v>12090</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9">
+      <c r="B9" s="4"/>
+      <c r="C9" s="5">
+        <f>SUM(C7:C8)</f>
+        <v>273.25</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="H9" s="59"/>
+    </row>
+    <row r="10" spans="2:9">
+      <c r="G10" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" s="58"/>
+      <c r="I10" s="9"/>
+    </row>
+    <row r="11" spans="2:9">
+      <c r="C11" s="48"/>
+      <c r="H11" s="59"/>
+    </row>
+    <row r="12" spans="2:9">
+      <c r="H12" s="59"/>
+    </row>
+    <row r="13" spans="2:9">
+      <c r="H13" s="59"/>
+    </row>
+    <row r="14" spans="2:9">
+      <c r="H14" s="25"/>
+    </row>
+    <row r="15" spans="2:9">
+      <c r="H15" s="25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CC03B67-503D-428C-82C4-722BB660D290}">
   <dimension ref="C5:H19"/>

--- a/დეკლარაცია დელივერერს.xlsx
+++ b/დეკლარაცია დელივერერს.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nana\bank-summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2185830-67FA-4156-B4E0-51ECD6042D56}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{884FB434-6D48-4BDD-9C82-06E495CFDC86}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" tabRatio="889" firstSheet="30" activeTab="44" xr2:uid="{262C77A9-C0EF-4E18-A530-ED4A8457AF6E}"/>
   </bookViews>
@@ -4858,21 +4858,22 @@
         <v>36</v>
       </c>
       <c r="C5" s="4">
-        <v>73348.649999999994</v>
+        <v>78442.710000000006</v>
       </c>
       <c r="D5" s="5">
         <f>C5/1.18</f>
-        <v>62159.872881355928</v>
+        <v>66476.872881355943</v>
       </c>
       <c r="E5" s="4">
         <f>D5*0.18</f>
-        <v>11188.777118644066</v>
+        <v>11965.837118644069</v>
       </c>
       <c r="G5" t="s">
         <v>4</v>
       </c>
       <c r="H5" s="5">
-        <v>10915</v>
+        <f>E6-0.99</f>
+        <v>11571.997118644069</v>
       </c>
     </row>
     <row r="6" spans="2:9">
@@ -4881,26 +4882,28 @@
       <c r="D6" s="5"/>
       <c r="E6" s="4">
         <f>E5-C9</f>
-        <v>10915.527118644066</v>
+        <v>11572.987118644069</v>
       </c>
       <c r="G6" t="s">
         <v>39</v>
       </c>
       <c r="H6" s="5">
-        <v>1175</v>
+        <v>1964.47</v>
       </c>
     </row>
     <row r="7" spans="2:9">
       <c r="B7" s="4"/>
       <c r="C7" s="4">
-        <v>75.83</v>
+        <v>195.43</v>
       </c>
       <c r="D7" s="56"/>
       <c r="E7" s="4"/>
       <c r="G7" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="5"/>
+      <c r="H7" s="5">
+        <v>2786.38</v>
+      </c>
     </row>
     <row r="8" spans="2:9">
       <c r="B8" s="4"/>
@@ -4911,14 +4914,14 @@
       <c r="E8" s="4"/>
       <c r="H8" s="58">
         <f>SUM(H5:H7)</f>
-        <v>12090</v>
+        <v>16322.847118644069</v>
       </c>
     </row>
     <row r="9" spans="2:9">
       <c r="B9" s="4"/>
       <c r="C9" s="5">
         <f>SUM(C7:C8)</f>
-        <v>273.25</v>
+        <v>392.85</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -4928,7 +4931,9 @@
       <c r="G10" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="H10" s="58"/>
+      <c r="H10" s="58">
+        <v>254</v>
+      </c>
       <c r="I10" s="9"/>
     </row>
     <row r="11" spans="2:9">
